--- a/Cards CSV.xlsx
+++ b/Cards CSV.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2db042c1c52e416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red5ad53519ae4fa3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,6 +46,12 @@
     <x:t xml:space="preserve">  </x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Khabib Nurmagomedov</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Islam Makhachev</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">The La+O1:O15st Stylebender</x:t>
   </x:si>
   <x:si>
@@ -58,6 +64,15 @@
     <x:t xml:space="preserve">Secret Juice</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Umar Nurmagomedov</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Father's Plan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Do Bronx</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">HP</x:t>
   </x:si>
   <x:si>
@@ -76,9 +91,24 @@
     <x:t xml:space="preserve">Gra</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Ste</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ste Ste Col</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Col</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ele</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Attack1 name</x:t>
   </x:si>
   <x:si>
@@ -115,12 +145,24 @@
     <x:t xml:space="preserve">Jab &amp; Teep</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Single Leg</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Koshi Guruma</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Roundhouse Kick</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Head Kick</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Calf Kick</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rear-Naked Choke</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Attack1 cost</x:t>
   </x:si>
   <x:si>
@@ -142,7 +184,16 @@
     <x:t xml:space="preserve">Col Col</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Water Col</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Water Col Col</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Fig Col</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ele Ele Col</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Attack1 damage</x:t>
@@ -177,6 +228,15 @@
 effect on volk just copy it)</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Flip a coin. If heads, this attack does 20 more damage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Choose a non-ex fighter named Khabib Nurmagomedov, Islam Makhachev, or Umar Nurmagomedov from your deck and put it on top of your deck.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The defending fighter is now Asleep.</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Attack2 name</x:t>
   </x:si>
   <x:si>
@@ -205,6 +265,12 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Underdog</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">From the Mountains of Caucasus</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ground Control</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Hatake</x:t>
@@ -218,6 +284,15 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Once per turn, if this fighter is in the active spot, you may look at the top card of your opponents deck.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">If your opponent has more points than you, this fighter's attacks do 30 more damage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As long as this fighter is in play, attacks from your Islam Makhachev and Umar Nurmagomedov cost 1 Colorless Energy less.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">As long as this fighter is in the active spot, your opponent's active fighter can't retreat.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">This fighter may use the attacks of any non-EX fighter on your bench. (As long as enery requirement is fulfilled)</x:t>
@@ -656,17 +731,18 @@
     <x:col min="10" max="10" width="15.33203125" customWidth="1"/>
     <x:col min="11" max="11" width="20.109375" customWidth="1"/>
     <x:col min="12" max="14" width="20.6640625" customWidth="1"/>
-    <x:col min="15" max="20" width="29.5546875" customWidth="1"/>
+    <x:col min="15" max="16" width="29.5546875" customWidth="1"/>
+    <x:col min="17" max="20" width="42" customWidth="1"/>
     <x:col min="21" max="21" width="21.6640625" customWidth="1"/>
     <x:col min="22" max="22" width="19.109375" customWidth="1"/>
     <x:col min="23" max="23" width="13.21875" customWidth="1"/>
     <x:col min="24" max="24" width="11.5546875" customWidth="1"/>
-    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="42" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="42" hidden="0" customWidth="1"/>
+    <x:col min="25" max="27" width="42" customWidth="1"/>
+    <x:col min="28" max="28" width="42" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="42" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="42" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="42" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -718,48 +794,66 @@
       <x:c r="P1" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
-        <x:v>Khabib Nurmagomedov</x:v>
-      </x:c>
-      <x:c r="R1" s="8" t="str">
-        <x:v>Islam Makhachev</x:v>
-      </x:c>
-      <x:c r="S1" s="8" t="str">
-        <x:v>Islam Makhachev</x:v>
-      </x:c>
-      <x:c r="T1" s="8" t="str">
-        <x:v>Islam Makhachev</x:v>
+      <x:c r="Q1" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R1" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S1" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="T1" s="3" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="U1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="V1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="W1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="X1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="Y1" s="8" t="str">
-        <x:v>Umar Nurmagomedov</x:v>
-      </x:c>
-      <x:c r="Z1" s="8" t="str">
-        <x:v>Father's Plan</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Y1" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Z1" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="AA1" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AB1" s="8" t="str">
+        <x:v>Chris Curtis</x:v>
+      </x:c>
+      <x:c r="AC1" s="8" t="str">
+        <x:v>Marcin Tybura</x:v>
+      </x:c>
+      <x:c r="AD1" s="8" t="str">
+        <x:v>Tommy McMillan</x:v>
+      </x:c>
+      <x:c r="AE1" s="8" t="str">
+        <x:v>Anshul Jubli</x:v>
+      </x:c>
+      <x:c r="AF1" s="8" t="str">
+        <x:v>Diego Lopes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B2" s="1">
         <x:v>110</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="n">
+      <x:c r="D2" s="1">
         <x:v>140</x:v>
       </x:c>
       <x:c r="E2" s="1">
@@ -778,7 +872,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="J2" s="1">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K2" s="1">
         <x:v>60</x:v>
@@ -796,16 +890,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="P2" s="1"/>
-      <x:c r="Q2" s="8" t="n">
+      <x:c r="Q2" s="3">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="R2" s="8" t="n">
+      <x:c r="R2" s="3">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="S2" s="8" t="n">
+      <x:c r="S2" s="3">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="T2" s="8" t="n">
+      <x:c r="T2" s="3">
         <x:v>140</x:v>
       </x:c>
       <x:c r="U2">
@@ -820,222 +914,304 @@
       <x:c r="X2">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="Y2" s="8" t="n">
+      <x:c r="Y2" s="3">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="Z2" s="8" t="str"/>
+      <x:c r="Z2" s="3"/>
+      <x:c r="AA2" s="3">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AB2" s="8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AC2" s="8" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="AD2" s="8" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AE2" s="8" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AF2" s="8" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="N3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P3" s="1"/>
-      <x:c r="Q3" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="R3" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="S3" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="T3" s="8" t="str">
-        <x:v>Water</x:v>
+      <x:c r="Q3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="T3" s="3" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U3" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="V3" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="W3" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="X3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="Y3" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="Z3" s="8" t="str">
-        <x:v>Item</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Y3" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Z3" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="AA3" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="AB3" s="8" t="str">
+        <x:v>Steel</x:v>
+      </x:c>
+      <x:c r="AC3" s="8" t="str">
+        <x:v>Steel</x:v>
+      </x:c>
+      <x:c r="AD3" s="8" t="str">
+        <x:v>Steel</x:v>
+      </x:c>
+      <x:c r="AE3" s="8" t="str">
+        <x:v>Grass</x:v>
+      </x:c>
+      <x:c r="AF3" s="8" t="str">
+        <x:v>Steel</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
       <x:c r="K4" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M4" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N4" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="O4" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="Q4" s="8" t="str">
-        <x:v>Single Leg</x:v>
-      </x:c>
-      <x:c r="R4" s="8" t="str">
-        <x:v>Jab</x:v>
-      </x:c>
-      <x:c r="S4" s="8" t="str">
-        <x:v>Soto Gari</x:v>
-      </x:c>
-      <x:c r="T4" s="8" t="str">
-        <x:v>Koshi Guruma</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="Q4" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S4" s="3" t="str">
+        <x:v>Calf Kick</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V4" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="W4" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="X4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="Y4" s="8" t="str">
-        <x:v>Calf Kick</x:v>
-      </x:c>
-      <x:c r="Z4" s="8" t="str"/>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="Y4" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Z4" s="3"/>
+      <x:c r="AA4" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AB4" s="8" t="str">
+        <x:v>Cross</x:v>
+      </x:c>
+      <x:c r="AC4" s="8" t="str">
+        <x:v>Heavy Cross</x:v>
+      </x:c>
+      <x:c r="AD4" s="8" t="str">
+        <x:v>Blitz</x:v>
+      </x:c>
+      <x:c r="AE4" s="8" t="str">
+        <x:v>DO NOT REDEEM!!!</x:v>
+      </x:c>
+      <x:c r="AF4" s="8" t="str">
+        <x:v>Uppercut</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
       <x:c r="K5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="N5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="1"/>
-      <x:c r="Q5" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="R5" s="8" t="str">
-        <x:v>Water</x:v>
-      </x:c>
-      <x:c r="S5" s="8" t="str">
-        <x:v>Water Col</x:v>
-      </x:c>
-      <x:c r="T5" s="8" t="str">
-        <x:v>Water Col</x:v>
+      <x:c r="Q5" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S5" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="T5" s="3" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V5" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="W5" t="s">
-        <x:v>44</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="X5" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="Y5" s="8" t="str">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="Y5" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Z5" s="3"/>
+      <x:c r="AA5" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="AB5" s="8" t="str">
+        <x:v>Steel Col</x:v>
+      </x:c>
+      <x:c r="AC5" s="8" t="str">
+        <x:v>Steel Col Col</x:v>
+      </x:c>
+      <x:c r="AD5" s="8" t="str">
         <x:v>Col</x:v>
       </x:c>
-      <x:c r="Z5" s="8" t="str"/>
+      <x:c r="AE5" s="8" t="str">
+        <x:v>Grass Col</x:v>
+      </x:c>
+      <x:c r="AF5" s="8" t="str">
+        <x:v>Steel Col</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>40</x:v>
@@ -1050,11 +1226,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H6" s="1">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="I6" s="1"/>
+      <x:c r="J6" s="1"/>
       <x:c r="K6">
         <x:v>0</x:v>
       </x:c>
@@ -1067,20 +1245,20 @@
       <x:c r="N6">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O6" t="n">
+      <x:c r="O6">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="Q6" s="8" t="n">
+      <x:c r="Q6" s="3">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="R6" s="8" t="n">
+      <x:c r="R6" s="3">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="S6" s="8" t="n">
+      <x:c r="S6" s="3">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="T6" s="8" t="n">
-        <x:v>80</x:v>
+      <x:c r="T6" s="3">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="V6">
         <x:v>0</x:v>
@@ -1091,60 +1269,87 @@
       <x:c r="X6">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="Y6" s="8" t="n">
+      <x:c r="Y6" s="3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="Z6" s="8" t="str"/>
+      <x:c r="Z6" s="3"/>
+      <x:c r="AA6" s="3">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="AB6" s="8" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="AC6" s="8" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AD6" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AE6" s="8" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AF6" s="8" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
-    <x:row r="7" ht="66" customHeight="1">
+    <x:row r="7" ht="52.79999923706055" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C7" s="6"/>
       <x:c r="D7" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5"/>
       <x:c r="G7" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>52</x:v>
-      </x:c>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I7" s="7"/>
       <x:c r="K7" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M7" s="3"/>
       <x:c r="N7" s="3"/>
-      <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="9" t="str"/>
-      <x:c r="S7" s="9" t="str"/>
-      <x:c r="T7" s="9" t="str">
-        <x:v>The defending fighter can't retreat during your opponent's next turn.</x:v>
-      </x:c>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+      <x:c r="S7" s="5"/>
+      <x:c r="T7" s="5"/>
       <x:c r="V7" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="Y7" s="9" t="str">
-        <x:v>Flip a coin. If heads, this attack does 20 more damage.</x:v>
-      </x:c>
-      <x:c r="Z7" s="9" t="str">
-        <x:v>Choose a non-ex fighter named Islam Makhachev or Umar Nurmagomedov from your deck and put it on top of your deck.</x:v>
-      </x:c>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Y7" s="5" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="Z7" s="5" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="AA7" s="5" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="AB7" s="9" t="str"/>
+      <x:c r="AC7" s="9" t="str"/>
+      <x:c r="AD7" s="9" t="str">
+        <x:v>Flip a coin until you get tails. This attack does 10 more damage for each heads.</x:v>
+      </x:c>
+      <x:c r="AE7" s="9" t="str"/>
+      <x:c r="AF7" s="9" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C8" s="1"/>
       <x:c r="D8" s="1"/>
@@ -1152,19 +1357,25 @@
       <x:c r="F8" s="1"/>
       <x:c r="G8" s="1"/>
       <x:c r="H8" s="1"/>
-      <x:c r="Q8" s="8" t="str"/>
-      <x:c r="R8" s="8" t="str"/>
-      <x:c r="S8" s="8" t="str"/>
-      <x:c r="T8" s="8" t="str"/>
-      <x:c r="Y8" s="8" t="str"/>
-      <x:c r="Z8" s="8" t="str"/>
+      <x:c r="Q8" s="3"/>
+      <x:c r="R8" s="3"/>
+      <x:c r="S8" s="3"/>
+      <x:c r="T8" s="3"/>
+      <x:c r="Y8" s="3"/>
+      <x:c r="Z8" s="3"/>
+      <x:c r="AA8" s="3"/>
+      <x:c r="AB8" s="8" t="str"/>
+      <x:c r="AC8" s="8" t="str"/>
+      <x:c r="AD8" s="8" t="str"/>
+      <x:c r="AE8" s="8" t="str"/>
+      <x:c r="AF8" s="8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
       <x:c r="D9" s="1"/>
@@ -1172,16 +1383,22 @@
       <x:c r="F9" s="1"/>
       <x:c r="G9" s="1"/>
       <x:c r="H9" s="1"/>
-      <x:c r="Q9" s="8" t="str"/>
-      <x:c r="R9" s="8" t="str"/>
-      <x:c r="S9" s="8" t="str"/>
-      <x:c r="T9" s="8" t="str"/>
-      <x:c r="Y9" s="8" t="str"/>
-      <x:c r="Z9" s="8" t="str"/>
+      <x:c r="Q9" s="3"/>
+      <x:c r="R9" s="3"/>
+      <x:c r="S9" s="3"/>
+      <x:c r="T9" s="3"/>
+      <x:c r="Y9" s="3"/>
+      <x:c r="Z9" s="3"/>
+      <x:c r="AA9" s="3"/>
+      <x:c r="AB9" s="8" t="str"/>
+      <x:c r="AC9" s="8" t="str"/>
+      <x:c r="AD9" s="8" t="str"/>
+      <x:c r="AE9" s="8" t="str"/>
+      <x:c r="AF9" s="8" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>40</x:v>
@@ -1192,19 +1409,25 @@
       <x:c r="F10" s="1"/>
       <x:c r="G10" s="1"/>
       <x:c r="H10" s="1"/>
-      <x:c r="Q10" s="8" t="str"/>
-      <x:c r="R10" s="8" t="str"/>
-      <x:c r="S10" s="8" t="str"/>
-      <x:c r="T10" s="8" t="str"/>
-      <x:c r="Y10" s="8" t="str"/>
-      <x:c r="Z10" s="8" t="str"/>
+      <x:c r="Q10" s="3"/>
+      <x:c r="R10" s="3"/>
+      <x:c r="S10" s="3"/>
+      <x:c r="T10" s="3"/>
+      <x:c r="Y10" s="3"/>
+      <x:c r="Z10" s="3"/>
+      <x:c r="AA10" s="3"/>
+      <x:c r="AB10" s="8" t="str"/>
+      <x:c r="AC10" s="8" t="str"/>
+      <x:c r="AD10" s="8" t="str"/>
+      <x:c r="AE10" s="8" t="str"/>
+      <x:c r="AF10" s="8" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C11" s="1"/>
       <x:c r="D11" s="1"/>
@@ -1212,22 +1435,28 @@
       <x:c r="F11" s="1"/>
       <x:c r="G11" s="1"/>
       <x:c r="H11" s="1"/>
-      <x:c r="Q11" s="8" t="str"/>
-      <x:c r="R11" s="8" t="str"/>
-      <x:c r="S11" s="8" t="str"/>
-      <x:c r="T11" s="8" t="str"/>
-      <x:c r="Y11" s="8" t="str"/>
-      <x:c r="Z11" s="8" t="str"/>
+      <x:c r="Q11" s="3"/>
+      <x:c r="R11" s="3"/>
+      <x:c r="S11" s="3"/>
+      <x:c r="T11" s="3"/>
+      <x:c r="Y11" s="3"/>
+      <x:c r="Z11" s="3"/>
+      <x:c r="AA11" s="3"/>
+      <x:c r="AB11" s="8" t="str"/>
+      <x:c r="AC11" s="8" t="str"/>
+      <x:c r="AD11" s="8" t="str"/>
+      <x:c r="AE11" s="8" t="str"/>
+      <x:c r="AF11" s="8" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D12" s="1"/>
       <x:c r="E12" s="1"/>
@@ -1235,54 +1464,74 @@
       <x:c r="G12" s="1"/>
       <x:c r="H12" s="1"/>
       <x:c r="O12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="Q12" s="8" t="str">
-        <x:v>From the Mountains of Caucasus</x:v>
-      </x:c>
-      <x:c r="R12" s="8" t="str"/>
-      <x:c r="S12" s="8" t="str"/>
-      <x:c r="T12" s="8" t="str"/>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="R12" s="3"/>
+      <x:c r="S12" s="3"/>
+      <x:c r="T12" s="3" t="s">
+        <x:v>86</x:v>
+      </x:c>
       <x:c r="U12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="Y12" s="8" t="str"/>
-      <x:c r="Z12" s="8" t="str"/>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="Y12" s="3"/>
+      <x:c r="Z12" s="3"/>
+      <x:c r="AA12" s="3"/>
+      <x:c r="AB12" s="8" t="str"/>
+      <x:c r="AC12" s="8" t="str"/>
+      <x:c r="AD12" s="8" t="str"/>
+      <x:c r="AE12" s="8" t="str"/>
+      <x:c r="AF12" s="8" t="str">
+        <x:v>Granite Chin</x:v>
+      </x:c>
     </x:row>
-    <x:row r="13" ht="66" customHeight="1">
+    <x:row r="13" ht="52.79999923706055" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D13" s="1"/>
       <x:c r="E13" s="1"/>
       <x:c r="F13" s="1"/>
       <x:c r="G13" s="1"/>
       <x:c r="H13" s="1"/>
-      <x:c r="O13" s="7" t="str">
-        <x:v>If your opponent has more points than you, this fighter's attacks do 30 more damage.</x:v>
+      <x:c r="O13" s="7" t="s">
+        <x:v>91</x:v>
       </x:c>
       <x:c r="P13" s="7"/>
-      <x:c r="Q13" s="8" t="str">
-        <x:v>As long as this fighter is in play, attacks from your Islam Makhachev and Umar Nurmagomedov cost 1 Colorless Energy less.</x:v>
-      </x:c>
-      <x:c r="R13" s="8" t="str"/>
-      <x:c r="S13" s="8" t="str"/>
-      <x:c r="T13" s="8" t="str"/>
+      <x:c r="Q13" s="3" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="R13" s="3"/>
+      <x:c r="S13" s="3"/>
+      <x:c r="T13" s="3" t="s">
+        <x:v>93</x:v>
+      </x:c>
       <x:c r="U13" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="Y13" s="8" t="str"/>
-      <x:c r="Z13" s="8" t="str"/>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="Y13" s="3"/>
+      <x:c r="Z13" s="3"/>
+      <x:c r="AA13" s="3"/>
+      <x:c r="AB13" s="8" t="str"/>
+      <x:c r="AC13" s="8" t="str"/>
+      <x:c r="AD13" s="8" t="str"/>
+      <x:c r="AE13" s="8" t="str"/>
+      <x:c r="AF13" s="8" t="str">
+        <x:v>This fighter takes 10 less damage from attacks.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1</x:v>
@@ -1318,16 +1567,16 @@
       <x:c r="O14">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q14" s="8" t="n">
+      <x:c r="Q14" s="3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="R14" s="8" t="n">
+      <x:c r="R14" s="3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S14" s="8" t="n">
+      <x:c r="S14" s="3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="T14" s="8" t="n">
+      <x:c r="T14" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="U14">
@@ -1342,153 +1591,219 @@
       <x:c r="X14">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Y14" s="8" t="n">
+      <x:c r="Y14" s="3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z14" s="8" t="str"/>
+      <x:c r="Z14" s="3"/>
+      <x:c r="AA14" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB14" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC14" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF14" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="L15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="N15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="P15" s="1"/>
-      <x:c r="Q15" s="8" t="str">
+      <x:c r="Q15" s="3" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="U15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="V15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="W15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="X15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="Y15" s="3" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="Z15" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="AA15" s="3" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="AB15" s="8" t="str">
         <x:v>Basic</x:v>
       </x:c>
-      <x:c r="R15" s="8" t="str">
-        <x:v>Prospect</x:v>
-      </x:c>
-      <x:c r="S15" s="8" t="str">
-        <x:v>Contender</x:v>
-      </x:c>
-      <x:c r="T15" s="8" t="str">
-        <x:v>Champion</x:v>
-      </x:c>
-      <x:c r="U15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="V15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="W15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="X15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="Y15" s="8" t="str">
+      <x:c r="AC15" s="8" t="str">
         <x:v>Basic</x:v>
       </x:c>
-      <x:c r="Z15" s="8" t="str">
-        <x:v>Item</x:v>
+      <x:c r="AD15" s="8" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="AE15" s="8" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="AF15" s="8" t="str">
+        <x:v>Basic</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N16" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="P16" s="1"/>
-      <x:c r="Q16" s="8" t="str">
+      <x:c r="Q16" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="U16" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="V16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="W16" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="X16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Y16" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="Z16" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AA16" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="AB16" s="8" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="AC16" s="8" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="AD16" s="8" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="AE16" s="8" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="AF16" s="8" t="str">
         <x:v>Rare</x:v>
-      </x:c>
-      <x:c r="R16" s="8" t="str">
-        <x:v>Common</x:v>
-      </x:c>
-      <x:c r="S16" s="8" t="str">
-        <x:v>Uncommon</x:v>
-      </x:c>
-      <x:c r="T16" s="8" t="str">
-        <x:v>Rare</x:v>
-      </x:c>
-      <x:c r="U16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="V16" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="W16" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X16" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="Y16" s="8" t="str">
-        <x:v>Uncommon</x:v>
-      </x:c>
-      <x:c r="Z16" s="8" t="str">
-        <x:v>Uncommon</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
